--- a/static/templates/contracts_template_en.xlsx
+++ b/static/templates/contracts_template_en.xlsx
@@ -77,6 +77,73 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Client name (must exist)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Maintenance Contract</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Single payment</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EL-0001, EL-0002</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>